--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VSC\tattoo_registry_server\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A5731DF-89ED-4301-A1A5-9FD71503817F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{672BBB6C-76EC-48B5-8258-AD4F21253B9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1211" uniqueCount="726">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1453" uniqueCount="762">
   <si>
     <t>ยศ</t>
   </si>
@@ -2214,6 +2214,114 @@
   </si>
   <si>
     <t>เลขประจำตัว 10 หลัก</t>
+  </si>
+  <si>
+    <t>ตำแหน่ง</t>
+  </si>
+  <si>
+    <t>ผบ.กรม ทพ.43</t>
+  </si>
+  <si>
+    <t>รอง ผบ.กรม ทพ.43</t>
+  </si>
+  <si>
+    <t>ฝอ.5 กรม ทพ.43</t>
+  </si>
+  <si>
+    <t>นายทหารฝ่ายส่งกำลังบำรุง กรม ทพ.43</t>
+  </si>
+  <si>
+    <t>ฝอ.2 กรม ทพ.43</t>
+  </si>
+  <si>
+    <t>ผบ.ร้อย.ทพ.กรม ทพ.43</t>
+  </si>
+  <si>
+    <t>ผช.นายทหารฝ่ายส่งกำลังบำรุง กรม ทพ.43</t>
+  </si>
+  <si>
+    <t>ผช.ฝอ.2 กรม ทพ.43</t>
+  </si>
+  <si>
+    <t>ผช.ฝยก.กรม ทพ.43</t>
+  </si>
+  <si>
+    <t>ผช.ฝอ.5 กรม ทพ.43</t>
+  </si>
+  <si>
+    <t>นกง.กรม ทพ.43</t>
+  </si>
+  <si>
+    <t>นธน.กรม ทพ.43</t>
+  </si>
+  <si>
+    <t>รอง ผบ.ร้อย.ทพ.กรม ทพ.43</t>
+  </si>
+  <si>
+    <t>ผช.นายทหารธุรการและกำลังพล กรม ทพ.43</t>
+  </si>
+  <si>
+    <t>นชง.กรม ทพ.43 และ รรก.จ่ากองร้อย (ชกท.001) บก.ร้อย.ร้อย.ทพ.กรม ทพ.43 (อัตรา จ.(พ.))</t>
+  </si>
+  <si>
+    <t>จ่ากองร้อย บก.ร้อย.ร้อย.ทพ.กรม ทพ.43</t>
+  </si>
+  <si>
+    <t>จ่ากรม บก.กรม กรม ทพ.43</t>
+  </si>
+  <si>
+    <t>นายสิบสื่อสาร บก.ร้อย.ร้อย.ทพ.กรม ทพ.43</t>
+  </si>
+  <si>
+    <t>นายสิบพยาบาล บก.ร้อย.ร้อย.ทพ.กรม ทพ.43</t>
+  </si>
+  <si>
+    <t>นายสิบส่งกำลังทั่วไป บก.ร้อย.ร้อย.ทพ.กรม ทพ.43</t>
+  </si>
+  <si>
+    <t>นายสิบธุรการและกำลังพล บก.ร้อย.ร้อย.ทพ.กรม ทพ.43</t>
+  </si>
+  <si>
+    <t>นายสิบยุทธการและการข่าว บก.ร้อย.ร้อย.ทพ.กรม ทพ.43</t>
+  </si>
+  <si>
+    <t>นายสิบส่งกำลังทั่วไป ฝกบ.กรม ทพ.43</t>
+  </si>
+  <si>
+    <t>นายสิบกำลังพล ฝกพ.กรม ทพ.43</t>
+  </si>
+  <si>
+    <t>นายสิบการข่าว ฝขว.กรม ทพ.43</t>
+  </si>
+  <si>
+    <t>นายสิบการเงิน บก.กรม กรม ทพ.43</t>
+  </si>
+  <si>
+    <t>นายสิบยุทธการ ฝยก.กรม ทพ.43</t>
+  </si>
+  <si>
+    <t>ช่างอาวุธ บก.กรม ทพ.43</t>
+  </si>
+  <si>
+    <t>พลขับรถ บก.กรม.กรม ทพ.43</t>
+  </si>
+  <si>
+    <t>นายสิบสื่อสาร บก.กรม กรม ทพ.43</t>
+  </si>
+  <si>
+    <t>ผบ.ชุดปฏิบัติการ ชป.ร้อย.ทพ.กรม ทพ.43</t>
+  </si>
+  <si>
+    <t>พลวิทยุ บก.กรม กรม ทพ.43</t>
+  </si>
+  <si>
+    <t>พลขับรถ บก.กรม กรม ทพ.43</t>
+  </si>
+  <si>
+    <t>นายสิบกิจการพลเรือน ฝกร.กรม ทพ.43</t>
+  </si>
+  <si>
+    <t>นายสิบพยาบาล บก.กรม กรม ทพ.43</t>
   </si>
 </sst>
 </file>
@@ -2543,21 +2651,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H242"/>
+  <dimension ref="A1:I242"/>
   <sheetFormatPr defaultRowHeight="21" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="1" customWidth="1"/>
     <col min="2" max="2" width="12" style="1" customWidth="1"/>
     <col min="3" max="3" width="11.140625" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="10.85546875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="9.140625" style="1"/>
-    <col min="8" max="8" width="22.28515625" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="9.140625" style="1"/>
+    <col min="5" max="5" width="77" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="10.85546875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="9.140625" style="1"/>
+    <col min="9" max="9" width="22.28515625" style="1" customWidth="1"/>
+    <col min="10" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>725</v>
       </c>
@@ -2571,13 +2680,16 @@
         <v>261</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>1433307567</v>
       </c>
@@ -2591,13 +2703,16 @@
         <v>263</v>
       </c>
       <c r="E2" s="1" t="s">
+        <v>727</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>1490801565</v>
       </c>
@@ -2611,13 +2726,16 @@
         <v>265</v>
       </c>
       <c r="E3" s="1" t="s">
+        <v>728</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>1290600247</v>
       </c>
@@ -2631,13 +2749,16 @@
         <v>267</v>
       </c>
       <c r="E4" s="1" t="s">
+        <v>729</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>1296803571</v>
       </c>
@@ -2651,13 +2772,16 @@
         <v>269</v>
       </c>
       <c r="E5" s="1" t="s">
+        <v>730</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="I5" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>1345700049</v>
       </c>
@@ -2671,13 +2795,16 @@
         <v>271</v>
       </c>
       <c r="E6" s="1" t="s">
+        <v>731</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="I6" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>1467600124</v>
       </c>
@@ -2691,13 +2818,16 @@
         <v>273</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H7" s="1" t="s">
+        <v>732</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I7" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>1352500006</v>
       </c>
@@ -2711,13 +2841,16 @@
         <v>275</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H8" s="1" t="s">
+        <v>732</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I8" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>1445601948</v>
       </c>
@@ -2731,13 +2864,16 @@
         <v>277</v>
       </c>
       <c r="E9" s="1" t="s">
+        <v>733</v>
+      </c>
+      <c r="F9" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="H9" s="1" t="s">
+      <c r="I9" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>1423000612</v>
       </c>
@@ -2751,13 +2887,16 @@
         <v>279</v>
       </c>
       <c r="E10" s="1" t="s">
+        <v>734</v>
+      </c>
+      <c r="F10" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="H10" s="1" t="s">
+      <c r="I10" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>1383600653</v>
       </c>
@@ -2771,13 +2910,16 @@
         <v>281</v>
       </c>
       <c r="E11" s="1" t="s">
+        <v>735</v>
+      </c>
+      <c r="F11" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="H11" s="1" t="s">
+      <c r="I11" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>1393600552</v>
       </c>
@@ -2791,13 +2933,16 @@
         <v>283</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H12" s="1" t="s">
+        <v>732</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I12" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <v>1522500752</v>
       </c>
@@ -2811,13 +2956,16 @@
         <v>285</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H13" s="1" t="s">
+        <v>732</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I13" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <v>1395700003</v>
       </c>
@@ -2831,13 +2979,16 @@
         <v>287</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H14" s="1" t="s">
+        <v>732</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I14" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <v>1461100737</v>
       </c>
@@ -2851,13 +3002,16 @@
         <v>289</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H15" s="1" t="s">
+        <v>732</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I15" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
         <v>1486500761</v>
       </c>
@@ -2871,13 +3025,16 @@
         <v>291</v>
       </c>
       <c r="E16" s="1" t="s">
+        <v>732</v>
+      </c>
+      <c r="F16" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="H16" s="1" t="s">
+      <c r="I16" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
         <v>1395600640</v>
       </c>
@@ -2891,13 +3048,16 @@
         <v>293</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H17" s="1" t="s">
+        <v>732</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I17" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
         <v>1453900582</v>
       </c>
@@ -2911,13 +3071,16 @@
         <v>295</v>
       </c>
       <c r="E18" s="1" t="s">
+        <v>732</v>
+      </c>
+      <c r="F18" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="H18" s="1" t="s">
+      <c r="I18" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
         <v>1433801049</v>
       </c>
@@ -2931,13 +3094,16 @@
         <v>297</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H19" s="1" t="s">
+        <v>736</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I19" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
         <v>1475700121</v>
       </c>
@@ -2951,13 +3117,16 @@
         <v>299</v>
       </c>
       <c r="E20" s="1" t="s">
+        <v>737</v>
+      </c>
+      <c r="F20" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="H20" s="1" t="s">
+      <c r="I20" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
         <v>1393200291</v>
       </c>
@@ -2971,13 +3140,16 @@
         <v>301</v>
       </c>
       <c r="E21" s="1" t="s">
+        <v>732</v>
+      </c>
+      <c r="F21" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="H21" s="1" t="s">
+      <c r="I21" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
         <v>1412201904</v>
       </c>
@@ -2991,13 +3163,16 @@
         <v>303</v>
       </c>
       <c r="E22" s="1" t="s">
+        <v>732</v>
+      </c>
+      <c r="F22" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="H22" s="1" t="s">
+      <c r="I22" s="1" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
         <v>1531101114</v>
       </c>
@@ -3011,13 +3186,16 @@
         <v>305</v>
       </c>
       <c r="E23" s="1" t="s">
+        <v>738</v>
+      </c>
+      <c r="F23" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="H23" s="1" t="s">
+      <c r="I23" s="1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
         <v>1363303432</v>
       </c>
@@ -3031,13 +3209,16 @@
         <v>307</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H24" s="1" t="s">
+        <v>732</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I24" s="1" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
         <v>1382203874</v>
       </c>
@@ -3051,13 +3232,16 @@
         <v>309</v>
       </c>
       <c r="E25" s="1" t="s">
+        <v>732</v>
+      </c>
+      <c r="F25" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="H25" s="1" t="s">
+      <c r="I25" s="1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A26" s="1">
         <v>1411400441</v>
       </c>
@@ -3071,13 +3255,16 @@
         <v>311</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H26" s="1" t="s">
+        <v>732</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I26" s="1" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A27" s="1">
         <v>1365601495</v>
       </c>
@@ -3091,13 +3278,16 @@
         <v>313</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H27" s="1" t="s">
+        <v>732</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I27" s="1" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A28" s="1">
         <v>1402100839</v>
       </c>
@@ -3111,13 +3301,16 @@
         <v>315</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H28" s="1" t="s">
+        <v>739</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I28" s="1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A29" s="1">
         <v>1443200039</v>
       </c>
@@ -3131,13 +3324,16 @@
         <v>317</v>
       </c>
       <c r="E29" s="1" t="s">
+        <v>739</v>
+      </c>
+      <c r="F29" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="H29" s="1" t="s">
+      <c r="I29" s="1" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A30" s="1">
         <v>1445700240</v>
       </c>
@@ -3151,13 +3347,16 @@
         <v>319</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H30" s="1" t="s">
+        <v>739</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I30" s="1" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A31" s="1">
         <v>2405600156</v>
       </c>
@@ -3171,13 +3370,16 @@
         <v>321</v>
       </c>
       <c r="E31" s="1" t="s">
+        <v>740</v>
+      </c>
+      <c r="F31" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="H31" s="1" t="s">
+      <c r="I31" s="1" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A32" s="1">
         <v>1326101146</v>
       </c>
@@ -3191,13 +3393,16 @@
         <v>323</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H32" s="1" t="s">
+        <v>739</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I32" s="1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A33" s="1">
         <v>1502501212</v>
       </c>
@@ -3211,13 +3416,16 @@
         <v>325</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H33" s="1" t="s">
+        <v>739</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I33" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A34" s="1">
         <v>1425600572</v>
       </c>
@@ -3231,13 +3439,16 @@
         <v>327</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H34" s="1" t="s">
+        <v>739</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I34" s="1" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A35" s="1">
         <v>1472201077</v>
       </c>
@@ -3251,13 +3462,16 @@
         <v>329</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H35" s="1" t="s">
+        <v>739</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I35" s="1" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A36" s="1">
         <v>1453600011</v>
       </c>
@@ -3271,13 +3485,16 @@
         <v>331</v>
       </c>
       <c r="E36" s="1" t="s">
+        <v>739</v>
+      </c>
+      <c r="F36" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="H36" s="1" t="s">
+      <c r="I36" s="1" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A37" s="1">
         <v>1316802379</v>
       </c>
@@ -3291,13 +3508,16 @@
         <v>333</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H37" s="1" t="s">
+        <v>741</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I37" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A38" s="1">
         <v>1455700368</v>
       </c>
@@ -3311,13 +3531,16 @@
         <v>335</v>
       </c>
       <c r="E38" s="1" t="s">
+        <v>739</v>
+      </c>
+      <c r="F38" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="H38" s="1" t="s">
+      <c r="I38" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A39" s="1">
         <v>1505601042</v>
       </c>
@@ -3331,13 +3554,16 @@
         <v>337</v>
       </c>
       <c r="E39" s="1" t="s">
+        <v>739</v>
+      </c>
+      <c r="F39" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="H39" s="1" t="s">
+      <c r="I39" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A40" s="1">
         <v>1503201051</v>
       </c>
@@ -3351,13 +3577,16 @@
         <v>339</v>
       </c>
       <c r="E40" s="1" t="s">
+        <v>739</v>
+      </c>
+      <c r="F40" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="H40" s="1" t="s">
+      <c r="I40" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A41" s="1">
         <v>1512501673</v>
       </c>
@@ -3371,13 +3600,16 @@
         <v>341</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H41" s="1" t="s">
+        <v>741</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I41" s="1" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A42" s="1">
         <v>1412201059</v>
       </c>
@@ -3391,13 +3623,16 @@
         <v>343</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H42" s="1" t="s">
+        <v>739</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I42" s="1" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A43" s="1">
         <v>3405600103</v>
       </c>
@@ -3411,13 +3646,16 @@
         <v>345</v>
       </c>
       <c r="E43" s="1" t="s">
+        <v>739</v>
+      </c>
+      <c r="F43" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="H43" s="1" t="s">
+      <c r="I43" s="1" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A44" s="1">
         <v>1313600724</v>
       </c>
@@ -3431,13 +3669,16 @@
         <v>347</v>
       </c>
       <c r="E44" s="1" t="s">
+        <v>741</v>
+      </c>
+      <c r="F44" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="H44" s="1" t="s">
+      <c r="I44" s="1" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A45" s="1">
         <v>1423600350</v>
       </c>
@@ -3451,13 +3692,16 @@
         <v>349</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H45" s="1" t="s">
+        <v>739</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I45" s="1" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A46" s="1">
         <v>1525601009</v>
       </c>
@@ -3471,13 +3715,16 @@
         <v>351</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H46" s="1" t="s">
+        <v>739</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I46" s="1" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A47" s="1">
         <v>1502202785</v>
       </c>
@@ -3491,13 +3738,16 @@
         <v>353</v>
       </c>
       <c r="E47" s="1" t="s">
+        <v>742</v>
+      </c>
+      <c r="F47" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="H47" s="1" t="s">
+      <c r="I47" s="1" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A48" s="1">
         <v>1422201062</v>
       </c>
@@ -3511,13 +3761,16 @@
         <v>355</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H48" s="1" t="s">
+        <v>742</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I48" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A49" s="1">
         <v>1385600103</v>
       </c>
@@ -3531,13 +3784,16 @@
         <v>357</v>
       </c>
       <c r="E49" s="1" t="s">
+        <v>742</v>
+      </c>
+      <c r="F49" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="H49" s="1" t="s">
+      <c r="I49" s="1" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A50" s="1">
         <v>1480300394</v>
       </c>
@@ -3551,13 +3807,16 @@
         <v>359</v>
       </c>
       <c r="E50" s="1" t="s">
+        <v>742</v>
+      </c>
+      <c r="F50" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="H50" s="1" t="s">
+      <c r="I50" s="1" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A51" s="1">
         <v>2485600089</v>
       </c>
@@ -3571,13 +3830,16 @@
         <v>361</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H51" s="1" t="s">
+        <v>743</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I51" s="1" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A52" s="1">
         <v>1503201043</v>
       </c>
@@ -3591,13 +3853,16 @@
         <v>363</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H52" s="1" t="s">
+        <v>742</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I52" s="1" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A53" s="1">
         <v>1413600483</v>
       </c>
@@ -3611,13 +3876,16 @@
         <v>365</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H53" s="1" t="s">
+        <v>742</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I53" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A54" s="1">
         <v>2434800030</v>
       </c>
@@ -3631,13 +3899,16 @@
         <v>367</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H54" s="1" t="s">
+        <v>742</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I54" s="1" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A55" s="1">
         <v>1422200004</v>
       </c>
@@ -3651,13 +3922,16 @@
         <v>339</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H55" s="1" t="s">
+        <v>742</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I55" s="1" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A56" s="1">
         <v>1411401038</v>
       </c>
@@ -3671,13 +3945,16 @@
         <v>370</v>
       </c>
       <c r="E56" s="1" t="s">
+        <v>742</v>
+      </c>
+      <c r="F56" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="H56" s="1" t="s">
+      <c r="I56" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A57" s="1">
         <v>1412200642</v>
       </c>
@@ -3691,13 +3968,16 @@
         <v>372</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H57" s="1" t="s">
+        <v>742</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I57" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A58" s="1">
         <v>2493200101</v>
       </c>
@@ -3711,13 +3991,16 @@
         <v>374</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H58" s="1" t="s">
+        <v>742</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I58" s="1" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A59" s="1">
         <v>1483600937</v>
       </c>
@@ -3731,13 +4014,16 @@
         <v>376</v>
       </c>
       <c r="E59" s="1" t="s">
+        <v>742</v>
+      </c>
+      <c r="F59" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="H59" s="1" t="s">
+      <c r="I59" s="1" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A60" s="1">
         <v>1503600071</v>
       </c>
@@ -3751,13 +4037,16 @@
         <v>378</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H60" s="1" t="s">
+        <v>744</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I60" s="1" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A61" s="1">
         <v>1582102071</v>
       </c>
@@ -3771,13 +4060,16 @@
         <v>380</v>
       </c>
       <c r="E61" s="1" t="s">
+        <v>745</v>
+      </c>
+      <c r="F61" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="H61" s="1" t="s">
+      <c r="I61" s="1" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A62" s="1">
         <v>1502501233</v>
       </c>
@@ -3791,13 +4083,16 @@
         <v>382</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H62" s="1" t="s">
+        <v>744</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I62" s="1" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A63" s="1">
         <v>1422200017</v>
       </c>
@@ -3811,13 +4106,16 @@
         <v>384</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H63" s="1" t="s">
+        <v>746</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I63" s="1" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A64" s="1">
         <v>1503600678</v>
       </c>
@@ -3831,13 +4129,16 @@
         <v>386</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H64" s="1" t="s">
+        <v>747</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I64" s="1" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A65" s="1">
         <v>1513200576</v>
       </c>
@@ -3851,13 +4152,16 @@
         <v>388</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H65" s="1" t="s">
+        <v>748</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I65" s="1" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A66" s="1">
         <v>1453200445</v>
       </c>
@@ -3871,13 +4175,16 @@
         <v>390</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H66" s="1" t="s">
+        <v>744</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I66" s="1" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A67" s="1">
         <v>1511400843</v>
       </c>
@@ -3891,13 +4198,16 @@
         <v>392</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H67" s="1" t="s">
+        <v>748</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I67" s="1" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A68" s="1">
         <v>1493200046</v>
       </c>
@@ -3911,13 +4221,16 @@
         <v>394</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H68" s="1" t="s">
+        <v>744</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I68" s="1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A69" s="1">
         <v>1452802388</v>
       </c>
@@ -3931,13 +4244,16 @@
         <v>396</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H69" s="1" t="s">
+        <v>749</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I69" s="1" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A70" s="1">
         <v>1423600360</v>
       </c>
@@ -3951,13 +4267,16 @@
         <v>398</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H70" s="1" t="s">
+        <v>747</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I70" s="1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A71" s="1">
         <v>1493600134</v>
       </c>
@@ -3971,13 +4290,16 @@
         <v>400</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H71" s="1" t="s">
+        <v>748</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I71" s="1" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A72" s="1">
         <v>1563601356</v>
       </c>
@@ -3991,13 +4313,16 @@
         <v>402</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H72" s="1" t="s">
+        <v>747</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I72" s="1" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A73" s="1">
         <v>1465700158</v>
       </c>
@@ -4011,13 +4336,16 @@
         <v>404</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H73" s="1" t="s">
+        <v>748</v>
+      </c>
+      <c r="F73" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I73" s="1" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A74" s="1">
         <v>1442500076</v>
       </c>
@@ -4031,13 +4359,16 @@
         <v>406</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H74" s="1" t="s">
+        <v>744</v>
+      </c>
+      <c r="F74" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I74" s="1" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A75" s="1">
         <v>1475600160</v>
       </c>
@@ -4051,13 +4382,16 @@
         <v>408</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H75" s="1" t="s">
+        <v>748</v>
+      </c>
+      <c r="F75" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I75" s="1" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A76" s="1">
         <v>1513601466</v>
       </c>
@@ -4071,13 +4405,16 @@
         <v>410</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H76" s="1" t="s">
+        <v>746</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I76" s="1" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A77" s="1">
         <v>1512202474</v>
       </c>
@@ -4091,13 +4428,16 @@
         <v>412</v>
       </c>
       <c r="E77" s="1" t="s">
+        <v>750</v>
+      </c>
+      <c r="F77" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="H77" s="1" t="s">
+      <c r="I77" s="1" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A78" s="1">
         <v>1433200221</v>
       </c>
@@ -4111,13 +4451,16 @@
         <v>414</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H78" s="1" t="s">
+        <v>744</v>
+      </c>
+      <c r="F78" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I78" s="1" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A79" s="1">
         <v>1517501459</v>
       </c>
@@ -4131,13 +4474,16 @@
         <v>416</v>
       </c>
       <c r="E79" s="1" t="s">
+        <v>751</v>
+      </c>
+      <c r="F79" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="H79" s="1" t="s">
+      <c r="I79" s="1" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A80" s="1">
         <v>2422500242</v>
       </c>
@@ -4151,13 +4497,16 @@
         <v>418</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H80" s="1" t="s">
+        <v>747</v>
+      </c>
+      <c r="F80" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I80" s="1" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A81" s="1">
         <v>1423600295</v>
       </c>
@@ -4171,13 +4520,16 @@
         <v>420</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H81" s="1" t="s">
+        <v>747</v>
+      </c>
+      <c r="F81" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I81" s="1" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A82" s="1">
         <v>1565601191</v>
       </c>
@@ -4191,13 +4543,16 @@
         <v>422</v>
       </c>
       <c r="E82" s="1" t="s">
+        <v>752</v>
+      </c>
+      <c r="F82" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="H82" s="1" t="s">
+      <c r="I82" s="1" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A83" s="1">
         <v>1491200415</v>
       </c>
@@ -4211,13 +4566,16 @@
         <v>424</v>
       </c>
       <c r="E83" s="1" t="s">
+        <v>748</v>
+      </c>
+      <c r="F83" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="H83" s="1" t="s">
+      <c r="I83" s="1" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A84" s="1">
         <v>1413600903</v>
       </c>
@@ -4231,13 +4589,16 @@
         <v>426</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H84" s="1" t="s">
+        <v>747</v>
+      </c>
+      <c r="F84" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I84" s="1" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A85" s="1">
         <v>1423600281</v>
       </c>
@@ -4251,13 +4612,16 @@
         <v>428</v>
       </c>
       <c r="E85" s="1" t="s">
+        <v>748</v>
+      </c>
+      <c r="F85" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="H85" s="1" t="s">
+      <c r="I85" s="1" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A86" s="1">
         <v>1504500797</v>
       </c>
@@ -4271,13 +4635,16 @@
         <v>430</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H86" s="1" t="s">
+        <v>746</v>
+      </c>
+      <c r="F86" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I86" s="1" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A87" s="1">
         <v>1515001253</v>
       </c>
@@ -4291,13 +4658,16 @@
         <v>432</v>
       </c>
       <c r="E87" s="1" t="s">
+        <v>744</v>
+      </c>
+      <c r="F87" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="H87" s="1" t="s">
+      <c r="I87" s="1" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A88" s="1">
         <v>1502500148</v>
       </c>
@@ -4311,13 +4681,16 @@
         <v>434</v>
       </c>
       <c r="E88" s="1" t="s">
+        <v>746</v>
+      </c>
+      <c r="F88" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="H88" s="1" t="s">
+      <c r="I88" s="1" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A89" s="1">
         <v>1465300348</v>
       </c>
@@ -4331,13 +4704,16 @@
         <v>436</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H89" s="1" t="s">
+        <v>746</v>
+      </c>
+      <c r="F89" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I89" s="1" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A90" s="1">
         <v>1502202783</v>
       </c>
@@ -4351,13 +4727,16 @@
         <v>438</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H90" s="1" t="s">
+        <v>747</v>
+      </c>
+      <c r="F90" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I90" s="1" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A91" s="1">
         <v>1421400845</v>
       </c>
@@ -4371,13 +4750,16 @@
         <v>440</v>
       </c>
       <c r="E91" s="1" t="s">
+        <v>746</v>
+      </c>
+      <c r="F91" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="H91" s="1" t="s">
+      <c r="I91" s="1" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A92" s="1">
         <v>1503600665</v>
       </c>
@@ -4391,13 +4773,16 @@
         <v>442</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H92" s="1" t="s">
+        <v>746</v>
+      </c>
+      <c r="F92" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I92" s="1" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A93" s="1">
         <v>1514501219</v>
       </c>
@@ -4411,13 +4796,16 @@
         <v>444</v>
       </c>
       <c r="E93" s="1" t="s">
+        <v>744</v>
+      </c>
+      <c r="F93" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="H93" s="1" t="s">
+      <c r="I93" s="1" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A94" s="1">
         <v>1533500129</v>
       </c>
@@ -4431,13 +4819,16 @@
         <v>446</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H94" s="1" t="s">
+        <v>747</v>
+      </c>
+      <c r="F94" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I94" s="1" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A95" s="1">
         <v>1452500011</v>
       </c>
@@ -4451,13 +4842,16 @@
         <v>448</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H95" s="1" t="s">
+        <v>746</v>
+      </c>
+      <c r="F95" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I95" s="1" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A96" s="1">
         <v>1493600123</v>
       </c>
@@ -4471,13 +4865,16 @@
         <v>450</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H96" s="1" t="s">
+        <v>746</v>
+      </c>
+      <c r="F96" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I96" s="1" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A97" s="1">
         <v>1554900346</v>
       </c>
@@ -4491,13 +4888,16 @@
         <v>452</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H97" s="1" t="s">
+        <v>753</v>
+      </c>
+      <c r="F97" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I97" s="1" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A98" s="1">
         <v>1503600680</v>
       </c>
@@ -4511,13 +4911,16 @@
         <v>454</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H98" s="1" t="s">
+        <v>748</v>
+      </c>
+      <c r="F98" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I98" s="1" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A99" s="1">
         <v>1553600273</v>
       </c>
@@ -4531,13 +4934,16 @@
         <v>456</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H99" s="1" t="s">
+        <v>746</v>
+      </c>
+      <c r="F99" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I99" s="1" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A100" s="1">
         <v>1513200583</v>
       </c>
@@ -4551,13 +4957,16 @@
         <v>458</v>
       </c>
       <c r="E100" s="1" t="s">
+        <v>747</v>
+      </c>
+      <c r="F100" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="H100" s="1" t="s">
+      <c r="I100" s="1" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A101" s="1">
         <v>1452202486</v>
       </c>
@@ -4571,13 +4980,16 @@
         <v>460</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H101" s="1" t="s">
+        <v>746</v>
+      </c>
+      <c r="F101" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I101" s="1" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A102" s="1">
         <v>1557104838</v>
       </c>
@@ -4591,13 +5003,16 @@
         <v>462</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H102" s="1" t="s">
+        <v>748</v>
+      </c>
+      <c r="F102" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I102" s="1" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A103" s="1">
         <v>1565600128</v>
       </c>
@@ -4611,13 +5026,16 @@
         <v>464</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H103" s="1" t="s">
+        <v>754</v>
+      </c>
+      <c r="F103" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I103" s="1" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A104" s="1">
         <v>1432203392</v>
       </c>
@@ -4631,13 +5049,16 @@
         <v>466</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H104" s="1" t="s">
+        <v>744</v>
+      </c>
+      <c r="F104" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I104" s="1" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A105" s="1">
         <v>1361400162</v>
       </c>
@@ -4651,13 +5072,16 @@
         <v>468</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H105" s="1" t="s">
+        <v>747</v>
+      </c>
+      <c r="F105" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I105" s="1" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A106" s="1">
         <v>1492202290</v>
       </c>
@@ -4671,13 +5095,16 @@
         <v>470</v>
       </c>
       <c r="E106" s="1" t="s">
+        <v>748</v>
+      </c>
+      <c r="F106" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="H106" s="1" t="s">
+      <c r="I106" s="1" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A107" s="1">
         <v>1503201042</v>
       </c>
@@ -4691,13 +5118,16 @@
         <v>471</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H107" s="1" t="s">
+        <v>747</v>
+      </c>
+      <c r="F107" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I107" s="1" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A108" s="1">
         <v>3492200044</v>
       </c>
@@ -4711,13 +5141,16 @@
         <v>473</v>
       </c>
       <c r="E108" s="1" t="s">
+        <v>744</v>
+      </c>
+      <c r="F108" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="H108" s="1" t="s">
+      <c r="I108" s="1" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A109" s="1">
         <v>1502501214</v>
       </c>
@@ -4731,13 +5164,16 @@
         <v>475</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H109" s="1" t="s">
+        <v>746</v>
+      </c>
+      <c r="F109" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I109" s="1" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A110" s="1">
         <v>1543201400</v>
       </c>
@@ -4751,13 +5187,16 @@
         <v>477</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H110" s="1" t="s">
+        <v>745</v>
+      </c>
+      <c r="F110" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I110" s="1" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A111" s="1">
         <v>1443600566</v>
       </c>
@@ -4771,13 +5210,16 @@
         <v>479</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H111" s="1" t="s">
+        <v>748</v>
+      </c>
+      <c r="F111" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I111" s="1" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A112" s="1">
         <v>1515401758</v>
       </c>
@@ -4791,13 +5233,16 @@
         <v>481</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H112" s="1" t="s">
+        <v>744</v>
+      </c>
+      <c r="F112" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I112" s="1" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A113" s="1">
         <v>1503600662</v>
       </c>
@@ -4811,13 +5256,16 @@
         <v>483</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H113" s="1" t="s">
+        <v>744</v>
+      </c>
+      <c r="F113" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I113" s="1" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A114" s="1">
         <v>1503600192</v>
       </c>
@@ -4831,13 +5279,16 @@
         <v>485</v>
       </c>
       <c r="E114" s="1" t="s">
+        <v>748</v>
+      </c>
+      <c r="F114" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="H114" s="1" t="s">
+      <c r="I114" s="1" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A115" s="1">
         <v>1451900125</v>
       </c>
@@ -4851,13 +5302,16 @@
         <v>487</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H115" s="1" t="s">
+        <v>744</v>
+      </c>
+      <c r="F115" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I115" s="1" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A116" s="1">
         <v>1563200832</v>
       </c>
@@ -4871,13 +5325,16 @@
         <v>489</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H116" s="1" t="s">
+        <v>747</v>
+      </c>
+      <c r="F116" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I116" s="1" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A117" s="1">
         <v>1466500491</v>
       </c>
@@ -4891,13 +5348,16 @@
         <v>491</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H117" s="1" t="s">
+        <v>746</v>
+      </c>
+      <c r="F117" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I117" s="1" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A118" s="1">
         <v>1502501210</v>
       </c>
@@ -4911,13 +5371,16 @@
         <v>493</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H118" s="1" t="s">
+        <v>747</v>
+      </c>
+      <c r="F118" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I118" s="1" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A119" s="1">
         <v>1502202790</v>
       </c>
@@ -4931,13 +5394,16 @@
         <v>495</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H119" s="1" t="s">
+        <v>755</v>
+      </c>
+      <c r="F119" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I119" s="1" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A120" s="1">
         <v>1544602654</v>
       </c>
@@ -4951,13 +5417,16 @@
         <v>497</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H120" s="1" t="s">
+        <v>747</v>
+      </c>
+      <c r="F120" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I120" s="1" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A121" s="1">
         <v>1565603089</v>
       </c>
@@ -4971,13 +5440,16 @@
         <v>499</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H121" s="1" t="s">
+        <v>746</v>
+      </c>
+      <c r="F121" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I121" s="1" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A122" s="1">
         <v>1485700093</v>
       </c>
@@ -4991,13 +5463,16 @@
         <v>501</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H122" s="1" t="s">
+        <v>744</v>
+      </c>
+      <c r="F122" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I122" s="1" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A123" s="1">
         <v>1502201722</v>
       </c>
@@ -5011,13 +5486,16 @@
         <v>503</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H123" s="1" t="s">
+        <v>746</v>
+      </c>
+      <c r="F123" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I123" s="1" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A124" s="1">
         <v>1562500685</v>
       </c>
@@ -5031,13 +5509,16 @@
         <v>505</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H124" s="1" t="s">
+        <v>756</v>
+      </c>
+      <c r="F124" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I124" s="1" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A125" s="1">
         <v>1461400354</v>
       </c>
@@ -5051,13 +5532,16 @@
         <v>506</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H125" s="1" t="s">
+        <v>748</v>
+      </c>
+      <c r="F125" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I125" s="1" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A126" s="1">
         <v>1501100176</v>
       </c>
@@ -5071,13 +5555,16 @@
         <v>508</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H126" s="1" t="s">
+        <v>744</v>
+      </c>
+      <c r="F126" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I126" s="1" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A127" s="1">
         <v>1512200308</v>
       </c>
@@ -5091,13 +5578,16 @@
         <v>510</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H127" s="1" t="s">
+        <v>746</v>
+      </c>
+      <c r="F127" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I127" s="1" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A128" s="1">
         <v>1565603096</v>
       </c>
@@ -5111,13 +5601,16 @@
         <v>511</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H128" s="1" t="s">
+        <v>747</v>
+      </c>
+      <c r="F128" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I128" s="1" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A129" s="1">
         <v>1502200385</v>
       </c>
@@ -5131,13 +5624,16 @@
         <v>513</v>
       </c>
       <c r="E129" s="1" t="s">
+        <v>747</v>
+      </c>
+      <c r="F129" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="H129" s="1" t="s">
+      <c r="I129" s="1" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A130" s="1">
         <v>1513201233</v>
       </c>
@@ -5151,13 +5647,16 @@
         <v>515</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H130" s="1" t="s">
+        <v>744</v>
+      </c>
+      <c r="F130" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I130" s="1" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A131" s="1">
         <v>1485600353</v>
       </c>
@@ -5171,13 +5670,16 @@
         <v>517</v>
       </c>
       <c r="E131" s="1" t="s">
+        <v>748</v>
+      </c>
+      <c r="F131" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="H131" s="1" t="s">
+      <c r="I131" s="1" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A132" s="1">
         <v>1445400900</v>
       </c>
@@ -5191,13 +5693,16 @@
         <v>519</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H132" s="1" t="s">
+        <v>748</v>
+      </c>
+      <c r="F132" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I132" s="1" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A133" s="1">
         <v>1585600712</v>
       </c>
@@ -5211,13 +5716,16 @@
         <v>520</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H133" s="1" t="s">
+        <v>748</v>
+      </c>
+      <c r="F133" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I133" s="1" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A134" s="1">
         <v>1463200007</v>
       </c>
@@ -5231,13 +5739,16 @@
         <v>522</v>
       </c>
       <c r="E134" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="F134" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="H134" s="1" t="s">
+      <c r="I134" s="1" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A135" s="1">
         <v>1533500113</v>
       </c>
@@ -5251,13 +5762,16 @@
         <v>524</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H135" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="F135" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I135" s="1" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A136" s="1">
         <v>2496600345</v>
       </c>
@@ -5271,13 +5785,16 @@
         <v>526</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H136" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="F136" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I136" s="1" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A137" s="1">
         <v>1502501217</v>
       </c>
@@ -5291,13 +5808,16 @@
         <v>527</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H137" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="F137" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I137" s="1" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A138" s="1">
         <v>1571303702</v>
       </c>
@@ -5311,13 +5831,16 @@
         <v>529</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H138" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="F138" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I138" s="1" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A139" s="1">
         <v>1593600024</v>
       </c>
@@ -5331,13 +5854,16 @@
         <v>531</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H139" s="1" t="s">
+        <v>745</v>
+      </c>
+      <c r="F139" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I139" s="1" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A140" s="1">
         <v>1512501186</v>
       </c>
@@ -5351,13 +5877,16 @@
         <v>533</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H140" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="F140" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I140" s="1" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A141" s="1">
         <v>2471400129</v>
       </c>
@@ -5371,13 +5900,16 @@
         <v>535</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H141" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="F141" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I141" s="1" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A142" s="1">
         <v>1493200489</v>
       </c>
@@ -5391,13 +5923,16 @@
         <v>537</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H142" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="F142" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I142" s="1" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A143" s="1">
         <v>1623200225</v>
       </c>
@@ -5411,13 +5946,16 @@
         <v>539</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H143" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="F143" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I143" s="1" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A144" s="1">
         <v>1543200433</v>
       </c>
@@ -5431,13 +5969,16 @@
         <v>541</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H144" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="F144" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I144" s="1" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A145" s="1">
         <v>1511400795</v>
       </c>
@@ -5451,13 +5992,16 @@
         <v>543</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H145" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="F145" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I145" s="1" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A146" s="1">
         <v>3526500179</v>
       </c>
@@ -5471,13 +6015,16 @@
         <v>545</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H146" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="F146" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I146" s="1" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A147" s="1">
         <v>1515602700</v>
       </c>
@@ -5491,13 +6038,16 @@
         <v>547</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H147" s="1" t="s">
+        <v>758</v>
+      </c>
+      <c r="F147" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I147" s="1" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A148" s="1">
         <v>1502200539</v>
       </c>
@@ -5511,13 +6061,16 @@
         <v>549</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H148" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="F148" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I148" s="1" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A149" s="1">
         <v>1472203078</v>
       </c>
@@ -5531,13 +6084,16 @@
         <v>551</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H149" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="F149" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I149" s="1" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="150" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A150" s="1">
         <v>1453200340</v>
       </c>
@@ -5551,13 +6107,16 @@
         <v>553</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H150" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="F150" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I150" s="1" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="151" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A151" s="1">
         <v>1601101329</v>
       </c>
@@ -5571,13 +6130,16 @@
         <v>554</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H151" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="F151" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I151" s="1" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="152" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A152" s="1">
         <v>1580800435</v>
       </c>
@@ -5591,13 +6153,16 @@
         <v>556</v>
       </c>
       <c r="E152" s="1" t="s">
+        <v>745</v>
+      </c>
+      <c r="F152" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="H152" s="1" t="s">
+      <c r="I152" s="1" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="153" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A153" s="1">
         <v>1583200092</v>
       </c>
@@ -5611,13 +6176,16 @@
         <v>558</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H153" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="F153" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I153" s="1" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="154" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A154" s="1">
         <v>1603601257</v>
       </c>
@@ -5631,13 +6199,16 @@
         <v>560</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H154" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="F154" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I154" s="1" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="155" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A155" s="1">
         <v>1543200430</v>
       </c>
@@ -5651,13 +6222,16 @@
         <v>562</v>
       </c>
       <c r="E155" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="F155" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="H155" s="1" t="s">
+      <c r="I155" s="1" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="156" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A156" s="1">
         <v>1553600271</v>
       </c>
@@ -5671,13 +6245,16 @@
         <v>564</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H156" s="1" t="s">
+        <v>759</v>
+      </c>
+      <c r="F156" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I156" s="1" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="157" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A157" s="1">
         <v>1563200852</v>
       </c>
@@ -5691,13 +6268,16 @@
         <v>566</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H157" s="1" t="s">
+        <v>749</v>
+      </c>
+      <c r="F157" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I157" s="1" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="158" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A158" s="1">
         <v>1552204103</v>
       </c>
@@ -5711,13 +6291,16 @@
         <v>568</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H158" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="F158" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I158" s="1" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="159" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A159" s="1">
         <v>1563601361</v>
       </c>
@@ -5731,13 +6314,16 @@
         <v>570</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H159" s="1" t="s">
+        <v>748</v>
+      </c>
+      <c r="F159" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I159" s="1" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="160" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A160" s="1">
         <v>1581400490</v>
       </c>
@@ -5751,13 +6337,16 @@
         <v>572</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H160" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="F160" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I160" s="1" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="161" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A161" s="1">
         <v>1533600416</v>
       </c>
@@ -5771,13 +6360,16 @@
         <v>574</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H161" s="1" t="s">
+        <v>759</v>
+      </c>
+      <c r="F161" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I161" s="1" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="162" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A162" s="1">
         <v>1552200322</v>
       </c>
@@ -5791,13 +6383,16 @@
         <v>576</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H162" s="1" t="s">
+        <v>744</v>
+      </c>
+      <c r="F162" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I162" s="1" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="163" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A163" s="1">
         <v>1563600062</v>
       </c>
@@ -5811,13 +6406,16 @@
         <v>578</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H163" s="1" t="s">
+        <v>744</v>
+      </c>
+      <c r="F163" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I163" s="1" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="164" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A164" s="1">
         <v>3521400053</v>
       </c>
@@ -5831,13 +6429,16 @@
         <v>579</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H164" s="1" t="s">
+        <v>748</v>
+      </c>
+      <c r="F164" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I164" s="1" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="165" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A165" s="1">
         <v>1543601488</v>
       </c>
@@ -5851,13 +6452,16 @@
         <v>581</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H165" s="1" t="s">
+        <v>744</v>
+      </c>
+      <c r="F165" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I165" s="1" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="166" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A166" s="1">
         <v>1607501816</v>
       </c>
@@ -5871,13 +6475,16 @@
         <v>583</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H166" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="F166" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I166" s="1" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="167" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A167" s="1">
         <v>2483200322</v>
       </c>
@@ -5891,13 +6498,16 @@
         <v>585</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H167" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="F167" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I167" s="1" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="168" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A168" s="1">
         <v>1473600161</v>
       </c>
@@ -5911,13 +6521,16 @@
         <v>586</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H168" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="F168" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I168" s="1" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="169" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A169" s="1">
         <v>1475700348</v>
       </c>
@@ -5931,13 +6544,16 @@
         <v>588</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H169" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="F169" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I169" s="1" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="170" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A170" s="1">
         <v>1551401144</v>
       </c>
@@ -5951,13 +6567,16 @@
         <v>590</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H170" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="F170" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I170" s="1" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="171" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A171" s="1">
         <v>2535600141</v>
       </c>
@@ -5971,13 +6590,16 @@
         <v>592</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H171" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="F171" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I171" s="1" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="172" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A172" s="1">
         <v>1475600057</v>
       </c>
@@ -5991,13 +6613,16 @@
         <v>594</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H172" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="F172" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I172" s="1" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="173" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A173" s="1">
         <v>1602500702</v>
       </c>
@@ -6011,13 +6636,16 @@
         <v>596</v>
       </c>
       <c r="E173" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="F173" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="H173" s="1" t="s">
+      <c r="I173" s="1" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="174" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A174" s="1">
         <v>1606502116</v>
       </c>
@@ -6031,13 +6659,16 @@
         <v>598</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H174" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="F174" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I174" s="1" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="175" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A175" s="1">
         <v>1602204034</v>
       </c>
@@ -6051,13 +6682,16 @@
         <v>599</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H175" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="F175" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I175" s="1" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="176" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A176" s="1">
         <v>1535601605</v>
       </c>
@@ -6071,13 +6705,16 @@
         <v>599</v>
       </c>
       <c r="E176" s="1" t="s">
+        <v>748</v>
+      </c>
+      <c r="F176" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="H176" s="1" t="s">
+      <c r="I176" s="1" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="177" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A177" s="1">
         <v>1580101017</v>
       </c>
@@ -6091,13 +6728,16 @@
         <v>602</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H177" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="F177" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I177" s="1" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="178" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A178" s="1">
         <v>1593200901</v>
       </c>
@@ -6111,13 +6751,16 @@
         <v>604</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H178" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="F178" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I178" s="1" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="179" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A179" s="1">
         <v>1602105079</v>
       </c>
@@ -6131,13 +6774,16 @@
         <v>605</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H179" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="F179" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I179" s="1" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="180" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A180" s="1">
         <v>1563601403</v>
       </c>
@@ -6151,13 +6797,16 @@
         <v>607</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H180" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="F180" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I180" s="1" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="181" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A181" s="1">
         <v>1503600021</v>
       </c>
@@ -6171,13 +6820,16 @@
         <v>608</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H181" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="F181" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I181" s="1" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="182" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A182" s="1">
         <v>1471400268</v>
       </c>
@@ -6191,13 +6843,16 @@
         <v>610</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H182" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="F182" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I182" s="1" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="183" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A183" s="1">
         <v>1565603087</v>
       </c>
@@ -6211,13 +6866,16 @@
         <v>612</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H183" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="F183" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I183" s="1" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="184" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A184" s="1">
         <v>1613601199</v>
       </c>
@@ -6231,13 +6889,16 @@
         <v>614</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H184" s="1" t="s">
+        <v>751</v>
+      </c>
+      <c r="F184" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I184" s="1" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="185" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A185" s="1">
         <v>1563200122</v>
       </c>
@@ -6251,13 +6912,16 @@
         <v>616</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H185" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="F185" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I185" s="1" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="186" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A186" s="1">
         <v>1560301721</v>
       </c>
@@ -6271,13 +6935,16 @@
         <v>618</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H186" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="F186" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I186" s="1" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="187" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A187" s="1">
         <v>1542500671</v>
       </c>
@@ -6291,13 +6958,16 @@
         <v>620</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H187" s="1" t="s">
+        <v>759</v>
+      </c>
+      <c r="F187" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I187" s="1" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="188" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A188" s="1">
         <v>1516500161</v>
       </c>
@@ -6311,13 +6981,16 @@
         <v>622</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H188" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="F188" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I188" s="1" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="189" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A189" s="1">
         <v>1603601263</v>
       </c>
@@ -6331,13 +7004,16 @@
         <v>624</v>
       </c>
       <c r="E189" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="F189" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="H189" s="1" t="s">
+      <c r="I189" s="1" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="190" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A190" s="1">
         <v>1613601204</v>
       </c>
@@ -6351,13 +7027,16 @@
         <v>626</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H190" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="F190" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I190" s="1" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="191" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A191" s="1">
         <v>1513600402</v>
       </c>
@@ -6371,13 +7050,16 @@
         <v>628</v>
       </c>
       <c r="E191" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="F191" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="H191" s="1" t="s">
+      <c r="I191" s="1" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="192" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A192" s="1">
         <v>1602601439</v>
       </c>
@@ -6391,13 +7073,16 @@
         <v>630</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H192" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="F192" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I192" s="1" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="193" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A193" s="1">
         <v>1515600295</v>
       </c>
@@ -6411,13 +7096,16 @@
         <v>632</v>
       </c>
       <c r="E193" s="1" t="s">
+        <v>744</v>
+      </c>
+      <c r="F193" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="H193" s="1" t="s">
+      <c r="I193" s="1" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="194" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A194" s="1">
         <v>2533200275</v>
       </c>
@@ -6431,13 +7119,16 @@
         <v>634</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H194" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="F194" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I194" s="1" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="195" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A195" s="1">
         <v>1554400240</v>
       </c>
@@ -6451,13 +7142,16 @@
         <v>636</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H195" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="F195" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I195" s="1" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="196" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A196" s="1">
         <v>1472201085</v>
       </c>
@@ -6471,13 +7165,16 @@
         <v>637</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H196" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="F196" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I196" s="1" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="197" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A197" s="1">
         <v>1621400599</v>
       </c>
@@ -6491,13 +7188,16 @@
         <v>639</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H197" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="F197" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I197" s="1" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="198" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A198" s="1">
         <v>1502201799</v>
       </c>
@@ -6511,13 +7211,16 @@
         <v>641</v>
       </c>
       <c r="E198" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="F198" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="H198" s="1" t="s">
+      <c r="I198" s="1" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="199" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A199" s="1">
         <v>1611303342</v>
       </c>
@@ -6531,13 +7234,16 @@
         <v>643</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H199" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="F199" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I199" s="1" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="200" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A200" s="1">
         <v>1517400694</v>
       </c>
@@ -6551,13 +7257,16 @@
         <v>645</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H200" s="1" t="s">
+        <v>748</v>
+      </c>
+      <c r="F200" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I200" s="1" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="201" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A201" s="1">
         <v>1582201780</v>
       </c>
@@ -6571,13 +7280,16 @@
         <v>647</v>
       </c>
       <c r="E201" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="F201" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="H201" s="1" t="s">
+      <c r="I201" s="1" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="202" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A202" s="1">
         <v>1556500386</v>
       </c>
@@ -6591,13 +7303,16 @@
         <v>649</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H202" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="F202" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I202" s="1" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="203" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A203" s="1">
         <v>2502500118</v>
       </c>
@@ -6611,13 +7326,16 @@
         <v>650</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H203" s="1" t="s">
+        <v>748</v>
+      </c>
+      <c r="F203" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I203" s="1" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="204" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A204" s="1">
         <v>1493200471</v>
       </c>
@@ -6631,13 +7349,16 @@
         <v>652</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H204" s="1" t="s">
+        <v>753</v>
+      </c>
+      <c r="F204" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I204" s="1" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="205" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A205" s="1">
         <v>1612203981</v>
       </c>
@@ -6651,13 +7372,16 @@
         <v>654</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H205" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="F205" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I205" s="1" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="206" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A206" s="1">
         <v>1567301400</v>
       </c>
@@ -6671,13 +7395,16 @@
         <v>656</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H206" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="F206" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I206" s="1" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="207" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A207" s="1">
         <v>1594500131</v>
       </c>
@@ -6691,13 +7418,16 @@
         <v>658</v>
       </c>
       <c r="E207" s="1" t="s">
+        <v>748</v>
+      </c>
+      <c r="F207" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="H207" s="1" t="s">
+      <c r="I207" s="1" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="208" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A208" s="1">
         <v>1594500592</v>
       </c>
@@ -6711,13 +7441,16 @@
         <v>660</v>
       </c>
       <c r="E208" s="1" t="s">
+        <v>744</v>
+      </c>
+      <c r="F208" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="H208" s="1" t="s">
+      <c r="I208" s="1" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="209" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A209" s="1">
         <v>1525501801</v>
       </c>
@@ -6731,13 +7464,16 @@
         <v>662</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H209" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="F209" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I209" s="1" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="210" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A210" s="1">
         <v>1491400155</v>
       </c>
@@ -6751,13 +7487,16 @@
         <v>664</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H210" s="1" t="s">
+        <v>744</v>
+      </c>
+      <c r="F210" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I210" s="1" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="211" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A211" s="1">
         <v>1563601355</v>
       </c>
@@ -6771,13 +7510,16 @@
         <v>666</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H211" s="1" t="s">
+        <v>744</v>
+      </c>
+      <c r="F211" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I211" s="1" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="212" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A212" s="1">
         <v>1562202376</v>
       </c>
@@ -6791,13 +7533,16 @@
         <v>668</v>
       </c>
       <c r="E212" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="F212" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="H212" s="1" t="s">
+      <c r="I212" s="1" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="213" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A213" s="1">
         <v>1565603091</v>
       </c>
@@ -6811,13 +7556,16 @@
         <v>670</v>
       </c>
       <c r="E213" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H213" s="1" t="s">
+        <v>744</v>
+      </c>
+      <c r="F213" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I213" s="1" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="214" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A214" s="1">
         <v>1565603095</v>
       </c>
@@ -6831,13 +7579,16 @@
         <v>672</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H214" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="F214" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I214" s="1" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="215" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A215" s="1">
         <v>1495501663</v>
       </c>
@@ -6851,13 +7602,16 @@
         <v>674</v>
       </c>
       <c r="E215" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H215" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="F215" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I215" s="1" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="216" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A216" s="1">
         <v>1451400559</v>
       </c>
@@ -6871,13 +7625,16 @@
         <v>676</v>
       </c>
       <c r="E216" s="1" t="s">
+        <v>760</v>
+      </c>
+      <c r="F216" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="H216" s="1" t="s">
+      <c r="I216" s="1" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="217" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A217" s="1">
         <v>1592201204</v>
       </c>
@@ -6891,13 +7648,16 @@
         <v>677</v>
       </c>
       <c r="E217" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="F217" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="H217" s="1" t="s">
+      <c r="I217" s="1" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="218" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A218" s="1">
         <v>1533301609</v>
       </c>
@@ -6911,13 +7671,16 @@
         <v>679</v>
       </c>
       <c r="E218" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="F218" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="H218" s="1" t="s">
+      <c r="I218" s="1" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="219" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A219" s="1">
         <v>1616802087</v>
       </c>
@@ -6931,13 +7694,16 @@
         <v>681</v>
       </c>
       <c r="E219" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="F219" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="H219" s="1" t="s">
+      <c r="I219" s="1" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="220" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A220" s="1">
         <v>1613201068</v>
       </c>
@@ -6951,13 +7717,16 @@
         <v>682</v>
       </c>
       <c r="E220" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H220" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="F220" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I220" s="1" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="221" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A221" s="1">
         <v>1502500991</v>
       </c>
@@ -6971,13 +7740,16 @@
         <v>684</v>
       </c>
       <c r="E221" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H221" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="F221" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I221" s="1" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="222" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A222" s="1">
         <v>2462200075</v>
       </c>
@@ -6991,13 +7763,16 @@
         <v>686</v>
       </c>
       <c r="E222" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H222" s="1" t="s">
+        <v>744</v>
+      </c>
+      <c r="F222" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I222" s="1" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="223" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A223" s="1">
         <v>1607104348</v>
       </c>
@@ -7011,13 +7786,16 @@
         <v>688</v>
       </c>
       <c r="E223" s="1" t="s">
+        <v>745</v>
+      </c>
+      <c r="F223" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="H223" s="1" t="s">
+      <c r="I223" s="1" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="224" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A224" s="1">
         <v>1563200005</v>
       </c>
@@ -7031,13 +7809,16 @@
         <v>690</v>
       </c>
       <c r="E224" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="F224" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="H224" s="1" t="s">
+      <c r="I224" s="1" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="225" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A225" s="1">
         <v>2552200468</v>
       </c>
@@ -7051,13 +7832,16 @@
         <v>691</v>
       </c>
       <c r="E225" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H225" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="F225" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I225" s="1" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="226" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A226" s="1">
         <v>1633500144</v>
       </c>
@@ -7071,13 +7855,16 @@
         <v>693</v>
       </c>
       <c r="E226" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H226" s="1" t="s">
+        <v>748</v>
+      </c>
+      <c r="F226" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I226" s="1" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="227" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A227" s="1">
         <v>1643500092</v>
       </c>
@@ -7091,13 +7878,16 @@
         <v>695</v>
       </c>
       <c r="E227" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H227" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="F227" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I227" s="1" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="228" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A228" s="1">
         <v>1635700298</v>
       </c>
@@ -7111,13 +7901,16 @@
         <v>697</v>
       </c>
       <c r="E228" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H228" s="1" t="s">
+        <v>748</v>
+      </c>
+      <c r="F228" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I228" s="1" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="229" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A229" s="1">
         <v>1644000732</v>
       </c>
@@ -7131,13 +7924,16 @@
         <v>699</v>
       </c>
       <c r="E229" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="F229" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="H229" s="1" t="s">
+      <c r="I229" s="1" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="230" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A230" s="1">
         <v>1652200684</v>
       </c>
@@ -7151,13 +7947,16 @@
         <v>701</v>
       </c>
       <c r="E230" s="1" t="s">
+        <v>748</v>
+      </c>
+      <c r="F230" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="H230" s="1" t="s">
+      <c r="I230" s="1" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="231" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A231" s="1">
         <v>1643200011</v>
       </c>
@@ -7171,13 +7970,16 @@
         <v>703</v>
       </c>
       <c r="E231" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="F231" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="H231" s="1" t="s">
+      <c r="I231" s="1" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="232" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A232" s="1">
         <v>1642200287</v>
       </c>
@@ -7191,13 +7993,16 @@
         <v>705</v>
       </c>
       <c r="E232" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H232" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="F232" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I232" s="1" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="233" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A233" s="1">
         <v>1635601116</v>
       </c>
@@ -7211,13 +8016,16 @@
         <v>707</v>
       </c>
       <c r="E233" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H233" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="F233" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I233" s="1" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="234" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A234" s="1">
         <v>1645601532</v>
       </c>
@@ -7231,13 +8039,16 @@
         <v>709</v>
       </c>
       <c r="E234" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H234" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="F234" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I234" s="1" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="235" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A235" s="1">
         <v>1643600126</v>
       </c>
@@ -7251,13 +8062,16 @@
         <v>711</v>
       </c>
       <c r="E235" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H235" s="1" t="s">
+        <v>748</v>
+      </c>
+      <c r="F235" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I235" s="1" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="236" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A236" s="1">
         <v>1635600030</v>
       </c>
@@ -7271,13 +8085,16 @@
         <v>713</v>
       </c>
       <c r="E236" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H236" s="1" t="s">
+        <v>748</v>
+      </c>
+      <c r="F236" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I236" s="1" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="237" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A237" s="1">
         <v>1601600832</v>
       </c>
@@ -7291,13 +8108,16 @@
         <v>715</v>
       </c>
       <c r="E237" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H237" s="1" t="s">
+        <v>759</v>
+      </c>
+      <c r="F237" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I237" s="1" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="238" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A238" s="1">
         <v>1663600462</v>
       </c>
@@ -7311,13 +8131,16 @@
         <v>717</v>
       </c>
       <c r="E238" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H238" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="F238" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I238" s="1" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="239" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A239" s="1">
         <v>1643600221</v>
       </c>
@@ -7331,13 +8154,16 @@
         <v>718</v>
       </c>
       <c r="E239" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H239" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="F239" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I239" s="1" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="240" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A240" s="1">
         <v>1663600552</v>
       </c>
@@ -7351,13 +8177,16 @@
         <v>720</v>
       </c>
       <c r="E240" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H240" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="F240" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I240" s="1" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="241" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A241" s="1">
         <v>1661400341</v>
       </c>
@@ -7371,13 +8200,16 @@
         <v>722</v>
       </c>
       <c r="E241" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H241" s="1" t="s">
+        <v>748</v>
+      </c>
+      <c r="F241" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I241" s="1" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="242" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A242" s="1">
         <v>1666500734</v>
       </c>
@@ -7391,9 +8223,12 @@
         <v>724</v>
       </c>
       <c r="E242" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H242" s="1" t="s">
+        <v>761</v>
+      </c>
+      <c r="F242" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I242" s="1" t="s">
         <v>255</v>
       </c>
     </row>
